--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
@@ -11,6 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,7 +465,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
         </is>
       </c>
     </row>
@@ -512,7 +513,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Назначение: Формирования документов</t>
+          <t>Назначение: Процесс подготовки документов (ncins). Источник правды по шагам: BPMN ump-prepare-documents-ncins-pa.bpmn (PR NCINS-143).</t>
         </is>
       </c>
     </row>
@@ -548,7 +549,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
         </is>
       </c>
     </row>
@@ -620,7 +621,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
         </is>
       </c>
     </row>
@@ -663,7 +664,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="108" customHeight="1">
+    <row r="6" ht="160" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
@@ -676,12 +677,19 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>[ump-prepare-documents-ncins-pa] Формирования документов: Start → Service Task get-application-data (GET /applications/{id}) → Service Task подготовка reportData для ПФ → Call Activity generate/save AlfaCapture (POST /documents/generate) → Service Task update-product (PUT /products/{id}, contractLink) → End.</t>
+          <t>[ump-prepare-documents-ncins-pa] Процесс подготовки документов (BPMN).
+Цепочка шагов (из BPMN):
+1) StartEvent
+2) Service Task service-task-get-params «Получить данные по заявке» — zeebe type get-application-data; input processType=PREPARE_DOCUMENTS (STATIC)
+3) Service Task service-task-get-report-data «Подготовить данные для ПФ» — type ump-prepare-documents-ncins-pa.get-report-data
+4) Call Activity call-activity-ump-generate-and-save-document-pa «Формирование и сохранение документа в AlfaCapture» — called process ump-generate-and-save-document-pa
+5) Service Task service-task-update-product «Обновить данные по продукту» — type update-product
+6) EndEvent</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Confluence/BPMN ump-prepare-documents-ncins-pa</t>
+          <t>Файл: bpmn/src/main/resources/ump-ncins-pa/ump-prepare-documents-ncins-pa.bpmn</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -708,7 +716,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Процесс синхронный. СА: единый SLA на sync-методы — несколько секунд на каждый вызов. Точное число — TBD с НТ.</t>
+          <t>Все шаги синхронные (service task / call activity). По ответам СА: единый SLA на sync — несколько секунд на вызов. Точное число — TBD с НТ.</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -727,7 +735,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>3</t>
@@ -740,12 +748,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>От общей базы 15000 заявок/мес. Среднее ≈ 89/час; макс (пик) ≈ 180/час. На заявку генерится 1 файл. Пример размера reportData/файла ≈ 283 КБ (avg/p95/max — TBD).</t>
+          <t>От общей базы 15000 заявок/мес (SFA, рабочие часы). Среднее ≈ 89/час; максимальное (пик ×2) ≈ 180/час. 1 документ на заявку. Пример размера файла/reportData ≈ 283 КБ (avg/p95/max — TBD).</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>15000/мес, рабочие часы; 1 документ на заявку</t>
+          <t>Способ: 15000/~21 р.д./8 ч ≈ 89/час; пик экспертно ×2</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -759,7 +767,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>4</t>
@@ -772,12 +780,12 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD (прогноз через 6 мес не зафиксирован командой)</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>TBD макс/среднее через 6 мес</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -791,7 +799,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
+    <row r="10" ht="126" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>5</t>
@@ -804,16 +812,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>[GET /applications/{id}] ump-application-facade ~89–180/час
-[Подготовка данных для ПФ / reportData] ~89–180/час
-[POST /documents/generate] OBIP+AlfaCapture ~89–180/час
-[PUT /products/{id}] ump-products ~89–180/час
+          <t>Сервис/метод | ЧПН (ср./пик, вызовов/час) — оценка от ЧПН процесса:
+[get-application-data] GET заявка ~89 / ~180
+[ump-prepare-documents-ncins-pa.get-report-data] подготовка ПФ ~89 / ~180
+[ump-generate-and-save-document-pa] Call Activity (генерация+AC) ~89 / ~180
+[update-product] обновление продукта ~89 / ~180
 Лимит параллелизма: 200 потоков (бэкенд)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Может совпадать с ЧПН процесса</t>
+          <t>Может совпадать с ЧПН процесса (каждый шаг 1 раз на заявку)</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -827,7 +836,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>6</t>
@@ -840,7 +849,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>TBD (пропорционально п.4)</t>
+          <t>TBD (пропорционально п.4). Пока ориентир = п.5.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -896,7 +905,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
         </is>
       </c>
     </row>
@@ -939,7 +948,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="126" customHeight="1">
+    <row r="6" ht="160" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>6</t>
@@ -952,15 +961,23 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>У воркера нет отдельного HTTP API процесса. Старт из main Call Activity / Camunda:
-variables: businessKey (DYNAMIC), productCode=NON_CREDIT_INSURANCE (const для продукта).
-Внутри: GET /applications/{id}?include=PARTICIPANT,PRODUCT — id=businessKey; include=STATIC.
-PUT /products/{id} — id=productId из заявки; в теле фактически значимо contractLink из AC.</t>
+          <t>У процесса нет HTTP-эндпоинта. Запуск через Camunda/Zeebe (из main Call Activity или напрямую).
+Входные переменные процесса на старте:
+- businessKey — DYNAMIC (UUID заявки)
+- productCode — передаётся на старте; для ncins фактически STATIC = NON_CREDIT_INSURANCE
+Маппинг Call Activity ump-generate-and-save-document-pa (из BPMN):
+- serviceId = businessKey (DYNAMIC)
+- serviceCode = "APPLICATION" (STATIC)
+- productCode = productCode (DYNAMIC_START / фактически const продукта)
+- documents = documents (DYNAMIC, из get-report-data)
+Outputs: docsResult←result, acRequestId, acDocuments
+get-application-data: input processType = PREPARE_DOCUMENTS (STATIC)
+update-product: type update-product (после AC)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Параметризация businessKey/заявок на объём ≥ ЧПН; productCode const.</t>
+          <t>Параметризация: набор businessKey ≥ ЧПН; productCode/serviceCode/processType — константы</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -974,7 +991,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
+    <row r="7" ht="108" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>7</t>
@@ -987,14 +1004,15 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Успех процесса: result=SUCCESS.
-get-application: getProcessParams=SUCCESS|ERROR.
-Ошибки генерации ПФ (бэкенд): HTTP 400 и 500 (полный каталог тел — у Жени/НИБ TBD).</t>
+          <t>Ожидаемый успешный ход: все task SUCCESS, процесс доходит до End.
+Call Activity возвращает: docsResult, acRequestId, acDocuments.
+Ошибки генерации ПФ/AC (из ответов бэкенда): HTTP 400 и 500 (полный каталог тел — TBD у Жени).
+get-application-data: getProcessParams=SUCCESS|ERROR (по процессной доке).</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>200/успех Camunda SUCCESS; 400/500 на generate</t>
+          <t>SUCCESS / ERROR; 400; 500</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1008,7 +1026,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>8</t>
@@ -1021,12 +1039,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>PUT /products/{id}: формально full update; по смыслу добавляется/обновляется поле contractLink (подтверждено бэкендом). Side effects сверх этого не выделялись.</t>
+          <t>Шаг update-product (type update-product): обновляет продукт; по ответам СА/бэкенда фактически значимо поле contractLink (формально PUT обновляет запись). Данные заявки читаются в get-application-data, не пишутся обратно в UMP кроме update-product.</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Обновляется contractLink у продукта</t>
+          <t>contractLink у продукта (+ поля product из маппинга update-product)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1040,7 +1058,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="50" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>9</t>
@@ -1072,7 +1090,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="54" customHeight="1">
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>10</t>
@@ -1085,12 +1103,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>ПФ/AlfaCapture — решение по мокам на стенде НТ уточнить (без AC своей папки реальное сохранение ограничено). Ошибки 400/500 иметь в негативных сценариях.</t>
+          <t>Внешние вызовы через Call Activity ump-generate-and-save-document-pa (ПФ + AlfaCapture). На НТ моки/доступ к AC уточнять: без своей папки AC реальное сохранение ограничено. get-application-data и update-product — внутренние job types UMP.</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Мок/стенд ПФ+AC по договорённости с НТ</t>
+          <t>Мок/стенд для ump-generate-and-save-document-pa при необходимости</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1104,7 +1122,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="50" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11</t>
@@ -1117,12 +1135,12 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Как у sync: несколько секунд на вызов (TBD точное значение с НТ).</t>
+          <t>Как у sync: несколько секунд на вызов (TBD точное значение с НТ), включая call activity generate/save.</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>generate/save ~несколько сек</t>
+          <t>get-report-data / generate-and-save / update-product — по несколько сек</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1136,7 +1154,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="72" customHeight="1">
+    <row r="12" ht="126" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>12</t>
@@ -1149,16 +1167,19 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>1) Success: get→prepare reportData→generate+save→PUT product→SUCCESS.
-2) GET 4xx → getProcessParams=ERROR.
-3) GET 5xx → 3 ретрая ×1с → инцидент.
-4) Generate 400/500.
-5) Пик в лимите 200 потоков.</t>
+          <t>Строго по BPMN (последовательность):
+1) Start
+2) get-application-data (processType=PREPARE_DOCUMENTS)
+3) ump-prepare-documents-ncins-pa.get-report-data
+4) Call Activity ump-generate-and-save-document-pa (serviceCode=APPLICATION)
+5) update-product
+6) End
+Негатив: ошибка get-application-data; ошибка generate 400/500; пик в лимите 200 потоков.</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Последовательные sync-вызовы внутри одного процесса на заявку</t>
+          <t>Один бизнес-процесс = последовательный вызов 4 исполняемых шагов</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1169,6 +1190,278 @@
       <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Аналитик</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>НТ пререквизиты :: Worker ump-prepare-documents-ncins-pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Шаги из ump-prepare-documents-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>BPMN id</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Type / called process</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Ключевые параметры</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>STATIC / DYNAMIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>StartEvent_1</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>startEvent</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>ожидает vars процесса</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>DYNAMIC_START: businessKey, productCode</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>service-task-get-params</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Получить данные по заявке</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>zeebe type: get-application-data</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>processType → PREPARE_DOCUMENTS</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>STATIC: processType=PREPARE_DOCUMENTS; DYNAMIC_START: businessKey (для GET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>service-task-get-report-data</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Подготовить данные для ПФ</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>type: ump-prepare-documents-ncins-pa.get-report-data</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>формирует documents/reportData</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>DYNAMIC_FROM_APP/PREV → documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>call-activity-ump-generate-and-save-document-pa</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Формирование и сохранение документа в AlfaCapture</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>calledElement: ump-generate-and-save-document-pa</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>serviceId=businessKey; serviceCode="APPLICATION"; productCode; documents; out: docsResult, acRequestId, acDocuments</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>STATIC: serviceCode=APPLICATION; DYNAMIC: serviceId, productCode, documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>service-task-update-product</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Обновить данные по продукту</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>type: update-product</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>после AC</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>DYNAMIC_FROM_PREV: acDocuments/links → product update</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Event_16wgp78</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>endEvent</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,34 +30,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4F6F7"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -74,27 +76,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -462,10 +472,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,7 +493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
@@ -510,18 +525,14 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Назначение: Процесс подготовки документов (ncins). Источник правды по шагам: BPMN ump-prepare-documents-ncins-pa.bpmn (PR NCINS-143).</t>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Назначение: Процесс подготовки документов (ncins). Источник правды: BPMN ump-prepare-documents-ncins-pa.bpmn (PR NCINS).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -532,11 +543,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -549,12 +564,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1 Согласование</t>
         </is>
@@ -585,11 +600,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -605,7 +615,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -621,259 +631,252 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. Минимальная информация для определения необходимости проведения НТ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="160" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="98" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>[ump-prepare-documents-ncins-pa] Процесс подготовки документов (BPMN).
-Цепочка шагов (из BPMN):
+Цепочка:
 1) StartEvent
-2) Service Task service-task-get-params «Получить данные по заявке» — zeebe type get-application-data; input processType=PREPARE_DOCUMENTS (STATIC)
-3) Service Task service-task-get-report-data «Подготовить данные для ПФ» — type ump-prepare-documents-ncins-pa.get-report-data
-4) Call Activity call-activity-ump-generate-and-save-document-pa «Формирование и сохранение документа в AlfaCapture» — called process ump-generate-and-save-document-pa
-5) Service Task service-task-update-product «Обновить данные по продукту» — type update-product
-6) EndEvent</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Файл: bpmn/src/main/resources/ump-ncins-pa/ump-prepare-documents-ncins-pa.bpmn</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+2) Service Task get-application-data — processType=PREPARE_DOCUMENTS (STATIC), businessKey (DYNAMIC)
+3) Service Task ump-prepare-documents-ncins-pa.get-report-data → documents/reportData
+4) Call Activity ump-generate-and-save-document-pa (serviceId=businessKey, serviceCode="APPLICATION" STATIC, productCode, documents)
+5) Service Task update-product → End
+MultiInstance на generate в финальном BPMN нет (Call Activity).</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Файл: bpmn/.../ump-prepare-documents-ncins-pa.bpmn</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Все шаги синхронные (service task / call activity). По ответам СА: единый SLA на sync — несколько секунд на вызов. Точное число — TBD с НТ.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Все шаги синхронные (service task / call activity). Ориентир СА: несколько секунд на вызов. Точное число — TBD с НТ.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>несколько секунд / sync-вызов (TBD мс)</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>От общей базы 15000 заявок/мес (SFA, рабочие часы). Среднее ≈ 89/час; максимальное (пик ×2) ≈ 180/час. 1 документ на заявку. Пример размера файла/reportData ≈ 283 КБ (avg/p95/max — TBD).</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Способ: 15000/~21 р.д./8 ч ≈ 89/час; пик экспертно ×2</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>От общей базы 15000 заявок/мес (SFA). Среднее ≈89/час; пик ≈180/час. 1 документ на заявку. Пример размера reportData ≈283 КБ (avg/p95/max — TBD).</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>15000/~21/8 ≈ 89/час; пик ×2</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>TBD (прогноз через 6 мес не зафиксирован командой)</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>TBD макс/среднее через 6 мес</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="126" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Сервис/метод | ЧПН (ср./пик, вызовов/час) — оценка от ЧПН процесса:
-[get-application-data] GET заявка ~89 / ~180
-[ump-prepare-documents-ncins-pa.get-report-data] подготовка ПФ ~89 / ~180
-[ump-generate-and-save-document-pa] Call Activity (генерация+AC) ~89 / ~180
-[update-product] обновление продукта ~89 / ~180
-Лимит параллелизма: 200 потоков (бэкенд)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Может совпадать с ЧПН процесса (каждый шаг 1 раз на заявку)</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>[get-application-data] ~89 / ~180
+[ump-prepare-documents-ncins-pa.get-report-data] ~89 / ~180
+[ump-generate-and-save-document-pa] (ПФ+AC) ~89 / ~180
+[update-product] ~89 / ~180</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Каждый шаг 1 раз на заявку</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>TBD (пропорционально п.4). Пока ориентир = п.5.</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>TBD (ориентир = п.5).</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -889,7 +892,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -905,300 +908,281 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2. Полная информация для проведения НТ (заполняется, только если получено заключение от инженера о необходимости проведения НТ)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Пререквизит</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Пример</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Где взять</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Предпочтительная роль заполняющего</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="160" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>У процесса нет HTTP-эндпоинта. Запуск через Camunda/Zeebe (из main Call Activity или напрямую).
-Входные переменные процесса на старте:
-- businessKey — DYNAMIC (UUID заявки)
-- productCode — передаётся на старте; для ncins фактически STATIC = NON_CREDIT_INSURANCE
-Маппинг Call Activity ump-generate-and-save-document-pa (из BPMN):
-- serviceId = businessKey (DYNAMIC)
-- serviceCode = "APPLICATION" (STATIC)
-- productCode = productCode (DYNAMIC_START / фактически const продукта)
-- documents = documents (DYNAMIC, из get-report-data)
-Outputs: docsResult←result, acRequestId, acDocuments
-get-application-data: input processType = PREPARE_DOCUMENTS (STATIC)
-update-product: type update-product (после AC)</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Параметризация: набор businessKey ≥ ЧПН; productCode/serviceCode/processType — константы</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>HTTP нет. Запуск Call Activity из main или напрямую в Zeebe.
+Старт vars: businessKey (DYNAMIC), productCode.
+Внутри: processType=PREPARE_DOCUMENTS (STATIC); Call Activity: serviceCode="APPLICATION" (STATIC FEEL).</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Параметризация businessKey ≥ ЧПН</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="108" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Ожидаемый успешный ход: все task SUCCESS, процесс доходит до End.
-Call Activity возвращает: docsResult, acRequestId, acDocuments.
-Ошибки генерации ПФ/AC (из ответов бэкенда): HTTP 400 и 500 (полный каталог тел — TBD у Жени).
-get-application-data: getProcessParams=SUCCESS|ERROR (по процессной доке).</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Успех: все task SUCCESS → End.
+Call Activity outs: docsResult, acRequestId, acDocuments.
+Ошибки ПФ/AC: HTTP 400/500 (полный каталог — TBD у Жени).</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>SUCCESS / ERROR; 400; 500</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Изменяемые данные в рамках работы метода</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Шаг update-product (type update-product): обновляет продукт; по ответам СА/бэкенда фактически значимо поле contractLink (формально PUT обновляет запись). Данные заявки читаются в get-application-data, не пишутся обратно в UMP кроме update-product.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>contractLink у продукта (+ поля product из маппинга update-product)</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>update-product: фактически значимо contractLink (PUT продукта). Заявка читается в get-application-data.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>contractLink (+ поля product из маппинга)</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Внешние вызовы через Call Activity ump-generate-and-save-document-pa (ПФ + AlfaCapture). На НТ моки/доступ к AC уточнять: без своей папки AC реальное сохранение ограничено. get-application-data и update-product — внутренние job types UMP.</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Мок/стенд для ump-generate-and-save-document-pa при необходимости</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Внешний вызов через Call Activity ump-generate-and-save-document-pa (ПФ + AlfaCapture). На НТ без своей папки AC реальное сохранение ограничено — уточнять мок/стенд.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Мок/стенд generate-and-save при необходимости</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Как у sync: несколько секунд на вызов (TBD точное значение с НТ), включая call activity generate/save.</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Как у sync: несколько секунд на вызов (TBD), включая call activity.</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>get-report-data / generate-and-save / update-product — по несколько сек</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Строго по BPMN (последовательность):
-1) Start
-2) get-application-data (processType=PREPARE_DOCUMENTS)
-3) ump-prepare-documents-ncins-pa.get-report-data
-4) Call Activity ump-generate-and-save-document-pa (serviceCode=APPLICATION)
-5) update-product
-6) End
-Негатив: ошибка get-application-data; ошибка generate 400/500; пик в лимите 200 потоков.</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Один бизнес-процесс = последовательный вызов 4 исполняемых шагов</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1) Start → get-application-data (PREPARE_DOCUMENTS) → get-report-data → Call Activity generate-and-save → update-product → End.
+2) Ошибка get 4xx/5xx.
+3) Ошибка генерации ПФ 400/500.
+4) Пик ~180/час, лимит потоков 200.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Последовательный вызов 4 исполняемых шагов</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1213,11 +1197,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1230,247 +1214,242 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN ump-prepare-documents-ncins-pa</t>
+          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Шаги из ump-prepare-documents-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>BPMN id</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Type / called process</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Ключевые параметры</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>STATIC / DYNAMIC</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>StartEvent_1</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>startEvent</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>ожидает vars процесса</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>DYNAMIC_START: businessKey, productCode</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>service-task-get-params</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Получить данные по заявке</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>zeebe type: get-application-data</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>processType → PREPARE_DOCUMENTS</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>STATIC: processType=PREPARE_DOCUMENTS; DYNAMIC_START: businessKey (для GET)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>STATIC: processType=PREPARE_DOCUMENTS; DYNAMIC: businessKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>service-task-get-report-data</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Подготовить данные для ПФ</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>type: ump-prepare-documents-ncins-pa.get-report-data</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>формирует documents/reportData</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>DYNAMIC_FROM_APP/PREV → documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC_FROM_APP → documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>call-activity-ump-generate-and-save-document-pa</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Формирование и сохранение документа в AlfaCapture</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Формирование и сохранение в AlfaCapture</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>calledElement: ump-generate-and-save-document-pa</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>serviceId=businessKey; serviceCode="APPLICATION"; productCode; documents; out: docsResult, acRequestId, acDocuments</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>STATIC: serviceCode=APPLICATION; DYNAMIC: serviceId, productCode, documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>STATIC: serviceCode; DYNAMIC: serviceId, productCode, documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>service-task-update-product</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>Обновить данные по продукту</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>type: update-product</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>после AC</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>DYNAMIC_FROM_PREV: acDocuments/links → product update</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>DYNAMIC_FROM_PREV → product update</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Event_16wgp78</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>End</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>endEvent</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>result=SUCCESS</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1. Согласование" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2. Минимальная информация" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3. Полная информация" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="BPMN методы (источник)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Методы и примеры (код)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +104,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -477,7 +478,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -493,7 +494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -525,10 +526,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Назначение: Процесс подготовки документов (ncins). Источник правды: BPMN ump-prepare-documents-ncins-pa.bpmn (PR NCINS).</t>
+          <t>BPMN ump-prepare-documents-ncins-pa + воркеры ApplicationData / PrepareDataForPrintForm / ProductDataUpdate + Call Activity generate-and-save.</t>
         </is>
       </c>
     </row>
@@ -548,7 +549,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -564,7 +565,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -615,7 +616,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -631,7 +632,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -674,203 +675,200 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="98" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Описание алгоритма работы тестируемого метода</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>[ump-prepare-documents-ncins-pa] Процесс подготовки документов (BPMN).
-Цепочка:
-1) StartEvent
-2) Service Task get-application-data — processType=PREPARE_DOCUMENTS (STATIC), businessKey (DYNAMIC)
-3) Service Task ump-prepare-documents-ncins-pa.get-report-data → documents/reportData
-4) Call Activity ump-generate-and-save-document-pa (serviceId=businessKey, serviceCode="APPLICATION" STATIC, productCode, documents)
-5) Service Task update-product → End
-MultiInstance на generate в финальном BPMN нет (Call Activity).</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Файл: bpmn/.../ump-prepare-documents-ncins-pa.bpmn</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>BPMN develop:
+1) get-application-data (processType=PREPARE_DOCUMENTS) → ApplicationDataWorker
+2) ump-prepare-documents-ncins-pa.get-report-data → PrepareDataForPrintFormWorker
+3) Call Activity ump-generate-and-save-document-pa (внешний процесс)
+4) update-product → ProductDataUpdateWorker (policyLink из acDocuments[0].acId)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>src/main/resources/bpmn/ump-prepare-documents-ncins-pa.bpmn</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Ссылка на алгоритм работы метода в git или confluence.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>SLA по времени отклика</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Все шаги синхронные (service task / call activity). Ориентир СА: несколько секунд на вызов. Точное число — TBD с НТ.</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>несколько секунд / sync-вызов (TBD мс)</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Все шаги sync (кроме внешнего Call Activity). Несколько секунд/вызов (TBD).</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>несколько сек</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Получить от заказчика доработки. Если заказчик неизвестен, определяем экспертно.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Частота планируемой нагрузки (ЧПН)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>От общей базы 15000 заявок/мес (SFA). Среднее ≈89/час; пик ≈180/час. 1 документ на заявку. Пример размера reportData ≈283 КБ (avg/p95/max — TBD).</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>15000/~21/8 ≈ 89/час; пик ×2</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>База нагрузки СА: 15000 заявок/мес SFA → ≈89/час среднее, пик ≈180/час. Timeout-ветки ~5% (из них ~95% signing). 1 документ/заявка.</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>89 / 180</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Аналитику нужно определить: 1) макс вызовов/час; 2) среднее вызовов/час; 3) способ получения оценки.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Само НТ проводится по профилю прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>[get-application-data] ~89 / ~180
-[ump-prepare-documents-ncins-pa.get-report-data] ~89 / ~180
-[ump-generate-and-save-document-pa] (ПФ+AC) ~89 / ~180
-[update-product] ~89 / ~180</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Каждый шаг 1 раз на заявку</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>[GET ump-application-facade /applications/{id}] ~89–180
+[get-report-data локально] ~89–180
+[Call Activity generate-and-save] ~89–180
+[PUT ump-products /products/{id}] ~89–180</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>applicationFacade.url / products.url</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с ЧПН.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Прогнозируемая через полгода ЧПН на вызываемые внутри тестируемого метода другие методы сервисов</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>TBD (ориентир = п.5).</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Может совпадать с прогнозируемой через полгода ЧПН.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -892,7 +890,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -908,7 +906,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
@@ -951,232 +949,238 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Пример кода вызова тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>HTTP нет. Запуск Call Activity из main или напрямую в Zeebe.
-Старт vars: businessKey (DYNAMIC), productCode.
-Внутри: processType=PREPARE_DOCUMENTS (STATIC); Call Activity: serviceCode="APPLICATION" (STATIC FEEL).</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Параметризация businessKey ≥ ЧПН</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Старт процесса / Call Activity из main.
+Шаг1 Camunda vars: {"businessKey":"550e8400-e29b-41d4-a716-446655110003","processType":"PREPARE_DOCUMENTS"}
+HTTP ApplicationDataWorker:
+GET {applicationFacade.url}/applications/{businessKey}?include=PARTICIPANT&amp;include=PRODUCT
+url prod-like: http://ump-application-facade.ump.svc.cluster.local
+Шаг2 get-report-data input (из IT): programId, fullName, inn, email, contractNumber, dates, sums, paymentAccount.
+Шаг4 update-product: productId, acDocuments[{type,acId}], productInfo.</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>IT: ApplicationDataWorkerIT, PrepareDataForPrintFormWorkerIT, ProductDataUpdateWorkerIT</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Тестировщик</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Примеры кода ответа тестируемого метода сервиса</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Успех: все task SUCCESS → End.
-Call Activity outs: docsResult, acRequestId, acDocuments.
-Ошибки ПФ/AC: HTTP 400/500 (полный каталог — TBD у Жени).</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>SUCCESS / ERROR; 400; 500</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>get-application-data: getProcessParams=SUCCESS + поля PREPARE_DOCUMENTS (productId, fullName, inn, contractNumber, …). Stub: stubs/ump/ump_application_response_200.json
+get-report-data out:
+{"serviceId":"&lt;businessKey&gt;","serviceCode":"APPLICATION","productCode":"NON_CREDIT_INSURANCE","documents":[{"documentType":"CONTRACT_ACCOUNT_BLOCK","reportData":"&lt;Base64 XML&gt;","isWriteInEa":false}]}
+update-product: {"getProcessParams":"SUCCESS"} (ERROR при exception).
+Ошибки facade → getProcessParams=ERROR.</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>SUCCESS / ERROR; XML в Base64</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Изменяемые данные в рамках работы метода</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>update-product: фактически значимо contractLink (PUT продукта). Заявка читается в get-application-data.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>contractLink (+ поля product из маппинга)</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Изменяемые данные в рамках работе метода</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>PUT /products/{id}: в productProperties.policyLink пишется acDocuments[0].acId (код ProductDataUpdateWorker).</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>policyLink = acId</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Перечислить поля/таблицы/ресурсы, которые создаются/перезаписываются (кроме логирования).</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Скрипт, содержащий сопутствующие изменения в БД (миграция)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Нет необходимости</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Опционально. Скрипт готовит разработчик только однажды перед боем.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Заглушки для внешних зависимостей</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Внешний вызов через Call Activity ump-generate-and-save-document-pa (ПФ + AlfaCapture). На НТ без своей папки AC реальное сохранение ограничено — уточнять мок/стенд.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Мок/стенд generate-and-save при необходимости</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Application facade и products — реальные Feign (на НТ WireMock/стенд). Call Activity generate-and-save — внешний процесс (ПФ+AC), мок/стенд уточнять.</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>WireMock как в IT</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Для зависимостей, которые нужно/можно глушить — прикрепить моки.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Ожидаемое время отклика замоканных внешних зависимостей</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Как у sync: несколько секунд на вызов (TBD), включая call activity.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>get-report-data / generate-and-save / update-product — по несколько сек</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Несколько секунд на sync-вызов (TBD).</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>несколько сек</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Потребуется для имитации нагрузки на внешние зависимости.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Разработчик</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Сценарий тестирования</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>1) Start → get-application-data (PREPARE_DOCUMENTS) → get-report-data → Call Activity generate-and-save → update-product → End.
-2) Ошибка get 4xx/5xx.
-3) Ошибка генерации ПФ 400/500.
-4) Пик ~180/час, лимит потоков 200.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Последовательный вызов 4 исполняемых шагов</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>1) Success: get→report→generate-save→update.
+2) facade error → ERROR.
+3) putProduct exception → ERROR.
+4) пик ~180/час.</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>IT покрывают шаги 1/2/4 частично</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Опционально. Готовит аналитик, если тестируется бизнес-процесс, а не метод.</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Аналитик</t>
         </is>
@@ -1193,15 +1197,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1214,14 +1218,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · актуализировано по BPMN PR (NCINS / commits 1–7)</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Шаги из ump-prepare-documents-ncins-pa.bpmn — STATIC vs DYNAMIC</t>
+          <t>Методы prepare — JobWorker + HTTP (develop + IT)</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1237,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN id</t>
+          <t>BPMN / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1243,209 +1247,145 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / called process</t>
+          <t>Type / HTTP</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ключевые параметры</t>
+          <t>Request / Input</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>STATIC / DYNAMIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+          <t>Response / Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>StartEvent_1</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Start</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>startEvent</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>ожидает vars процесса</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC_START: businessKey, productCode</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>get-application-data</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>GET /applications/{id}?include=PARTICIPANT&amp;include=PRODUCT</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>{"businessKey":"550e8400-...","processType":"PREPARE_DOCUMENTS"}</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>ApplicationResponseDto → getProcessParams=SUCCESS + product fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>service-task-get-params</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Получить данные по заявке</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>zeebe type: get-application-data</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>processType → PREPARE_DOCUMENTS</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>STATIC: processType=PREPARE_DOCUMENTS; DYNAMIC: businessKey</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ump-prepare-documents-ncins-pa.get-report-data</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>PrepareDataForPrintFormWorker</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>нет HTTP (XML+Base64)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>fullName/inn/email/contractNumber/sums/paymentAccount (IT)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>documents[0].documentType=CONTRACT_ACCOUNT_BLOCK, reportData=Base64</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>service-task-get-report-data</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Подготовить данные для ПФ</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>type: ump-prepare-documents-ncins-pa.get-report-data</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>формирует documents/reportData</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC_FROM_APP → documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Call Activity</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ump-generate-and-save-document-pa</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>внешний процесс</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>serviceId=businessKey, serviceCode=APPLICATION, documents</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>acDocuments, acRequestId, docsResult</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>call-activity-ump-generate-and-save-document-pa</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Формирование и сохранение в AlfaCapture</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>calledElement: ump-generate-and-save-document-pa</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>serviceId=businessKey; serviceCode="APPLICATION"; productCode; documents; out: docsResult, acRequestId, acDocuments</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>STATIC: serviceCode; DYNAMIC: serviceId, productCode, documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>service-task-update-product</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Обновить данные по продукту</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>type: update-product</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>после AC</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>DYNAMIC_FROM_PREV → product update</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>endEvent</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>result=SUCCESS</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>update-product</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ProductDataUpdateWorker</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>PUT /products/{id}</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>{"productId":"660e...","acDocuments":[{"type":"CONTRACT_ACCOUNT_BLOCK","acId":"770e..."}],"productInfo":{}}</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>{"getProcessParams":"SUCCESS"}</t>
         </is>
       </c>
     </row>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
@@ -885,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -906,7 +906,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="220" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>6</t>
@@ -962,23 +962,64 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Старт процесса / Call Activity из main.
-Шаг1 Camunda vars: {"businessKey":"550e8400-e29b-41d4-a716-446655110003","processType":"PREPARE_DOCUMENTS"}
-HTTP ApplicationDataWorker:
-GET {applicationFacade.url}/applications/{businessKey}?include=PARTICIPANT&amp;include=PRODUCT
-url prod-like: http://ump-application-facade.ump.svc.cluster.local
-Шаг2 get-report-data input (из IT): programId, fullName, inn, email, contractNumber, dates, sums, paymentAccount.
-Шаг4 update-product: productId, acDocuments[{type,acId}], productInfo.</t>
+          <t xml:space="preserve">У воркера отсутствует HTTP-эндпоинт.
+Вызов происходит напрямую в Camunda.
+Camunda на базе Java скрипта, инструкция — https://confluence.moscow.alfaintra.net/pages/viewpage.action?pageId=2136656813
+Пример запроса:
+Map&lt;String, Object&gt; variables = Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110003", // id заявки (UMP application)
+  "productCode", "NON_CREDIT_INSURANCE" // const
+);
+final ProcessInstanceEvent processInstanceEvent = client
+  .newCreateInstanceCommand()
+  .bpmnProcessId("ump-prepare-documents-ncins-pa")
+  .latestVersion()
+  .variables(variables)
+  .send()
+  .join();
+Параметры для запроса:
+1. businessKey — UUID заявки (параметризовать на объём ≥ ЧПН)
+2. productCode — const NON_CREDIT_INSURANCE (параметризация не нужна)
+--- Внутренние вызовы воркеров (из кода/IT) ---
+1) ApplicationDataWorker type=get-application-data
+Camunda job vars:
+Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110003",
+  "processType", "PREPARE_DOCUMENTS" // STATIC в BPMN
+);
+HTTP:
+GET {applicationFacade.url}/applications/550e8400-e29b-41d4-a716-446655110003?include=PARTICIPANT&amp;include=PRODUCT
+Host example: http://ump-application-facade.ump.svc.cluster.local
+2) PrepareDataForPrintFormWorker type=ump-prepare-documents-ncins-pa.get-report-data
+Вход (IT PrepareDataForPrintFormWorkerIT) — поля заявки:
+programId=1, fullName="Иванов Иван Иванович", inn="123456789012",
+email="ivanov@example.com", contractNumber="NC-2025-001",
+beginDate/endDate, currentDate="2025-01-15",
+insuranceSum=1000000.0, insurancePremium=50000.0,
+paymentAccount="40817810000000000001"
+3) Call Activity ump-generate-and-save-document-pa (внешний)
+serviceId=businessKey, serviceCode="APPLICATION", productCode, documents
+4) ProductDataUpdateWorker type=update-product
+Map.of(
+  "businessKey", "550e8400-e29b-41d4-a716-446655110000",
+  "productId", "3d9fe175-2bc5-442a-b900-48522551de3f",
+  "acDocuments", "[{ "type": "CONTRACT_ACCOUNT_BLOCK", "acId": "770e8400-e29b-41d4-a716-446655110002" }]",
+  "productInfo", "{}"
+);
+HTTP: PUT {products.url}/products/3d9fe175-2bc5-442a-b900-48522551de3f
+</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>IT: ApplicationDataWorkerIT, PrepareDataForPrintFormWorkerIT, ProductDataUpdateWorkerIT</t>
+          <t>Map.of start + GET applications + PUT products (IT)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.</t>
+          <t>Сначала нужно добыть живой пример вызова сервиса (локально/стенд) и параметризовать.
+Параметризовать businessKey (≥ ЧПН). productCode — const NON_CREDIT_INSURANCE.
+Источник примеров: develop ump-ncins-pa *WorkerIT + stubs.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -987,7 +1028,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="70" customHeight="1">
+    <row r="7" ht="180" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>7</t>
@@ -1000,21 +1041,48 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>get-application-data: getProcessParams=SUCCESS + поля PREPARE_DOCUMENTS (productId, fullName, inn, contractNumber, …). Stub: stubs/ump/ump_application_response_200.json
-get-report-data out:
-{"serviceId":"&lt;businessKey&gt;","serviceCode":"APPLICATION","productCode":"NON_CREDIT_INSURANCE","documents":[{"documentType":"CONTRACT_ACCOUNT_BLOCK","reportData":"&lt;Base64 XML&gt;","isWriteInEa":false}]}
-update-product: {"getProcessParams":"SUCCESS"} (ERROR при exception).
-Ошибки facade → getProcessParams=ERROR.</t>
+          <t>1) get-application-data
+Camunda out: getProcessParams = SUCCESS (+ поля PREPARE_DOCUMENTS).
+HTTP 200 stub stubs/ump/ump_application_response_200.json (фрагмент):
+{
+  "id": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "participants": [{ "fullName": "ООО Звезда", "inn": "7826688577", ... }],
+  "products": [{
+    "id": "3d9fe175-2bc5-442a-b900-48522551de3f",
+    "code": "NON_CREDIT_INSURANCE",
+    "productProperties": {
+      "contractNumber": "1423423/sdf/123",
+      "insuranceSum": 20000.0,
+      "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9"
+    }
+  }]
+}
+Ошибка: getProcessParams = ERROR
+2) get-report-data out:
+{
+  "serviceId": "550e8400-e29b-41d4-a716-446655110003",
+  "serviceCode": "APPLICATION",
+  "productCode": "NON_CREDIT_INSURANCE",
+  "documents": [{
+    "documentType": "CONTRACT_ACCOUNT_BLOCK",
+    "reportData": "&lt;Base64(XML datasource)&gt;",
+    "isWriteInEa": false
+  }]
+}
+3) update-product out: { "getProcessParams": "SUCCESS" }
+   при exception putProduct: { "getProcessParams": "ERROR" }</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>SUCCESS / ERROR; XML в Base64</t>
+          <t>getProcessParams=SUCCESS; HTTP 200; documents[].reportData</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Нужны примеры ответов, которые можно считать ожидаемыми.</t>
+          <t>Нужны примеры ответов, которые можно считать ожидаемыми.
+Например: getProcessParams=SUCCESS; HTTP 200/201; result=SUCCESS.
+Источник: *WorkerIT + stubs/ump/ump_application_response_200.json.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1186,6 +1254,14 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
+++ b/nt-prerequisites-xlsx/НТ пререквизиты __ Worker ump-prepare-documents-ncins-pa.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
       <name val="Calibri"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -93,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,6 +110,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -494,7 +501,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -565,7 +572,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -632,7 +639,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -885,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -906,7 +913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of)</t>
+          <t>UMP · п.6/п.7 в формате образца onboarding (Map.of) · полные HTTP body</t>
         </is>
       </c>
     </row>
@@ -1254,14 +1261,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1277,11 +1276,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1294,14 +1293,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UMP · 21 июля 2026 · код develop ump-ncins-pa@4a921a1653e + IT stubs</t>
+          <t>Полные request/response (не только имя метода). Источник: develop ump-ncins-pa@4a921a1653e + *WorkerIT + stubs. · полные HTTP body</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Методы prepare — JobWorker + HTTP (develop + IT)</t>
+          <t>HTTP / JobWorker — полные тела запросов и ответов</t>
         </is>
       </c>
     </row>
@@ -1313,155 +1312,392 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>BPMN / JobWorker</t>
+          <t>Метод / JobWorker</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Где</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Type / HTTP</t>
+          <t>Полный REQUEST (headers + body)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Request / Input</t>
+          <t>Полный RESPONSE (status + body)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Response / Output</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="70" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="420" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>get-application-data</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>ApplicationDataWorker</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>GET /applications/{id}?include=PARTICIPANT&amp;include=PRODUCT</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>{"businessKey":"550e8400-...","processType":"PREPARE_DOCUMENTS"}</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>ApplicationResponseDto → getProcessParams=SUCCESS + product fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="70" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>get-application-data
+GET /applications/{id}</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorker
+все процессы</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>GET /applications/6dc5daf3-da12-4aae-9766-572da7b6b003?include=PARTICIPANT&amp;include=PRODUCT HTTP/1.1
+Host: ump-application-facade.ump.svc.cluster.local
+Accept: application/json
+(без body)
+Camunda job input:
+{
+  "businessKey": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "processType": "&lt;PREPARE_DOCUMENTS|SIGNING|PAYMENT|FINALISATION|DELETE_DOCS&gt;"
+}</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: application/json
+{
+  "externalApplicationIds": [
+    {
+      "extAppId": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+      "systemCode": "SFA",
+      "extAppCreateDate": "2026-06-25T12:45:34.785179Z"
+    }
+  ],
+  "channels": [
+    {
+      "id": "bd458000-77c2-48af-91b4-815f7ef2d4e6",
+      "userInfo": {
+        "userId": "f6753df0-b5c9-4828-a7b7-f9f3f7d8f33c",
+        "login": "service-account-nib-corp-ncins"
+      },
+      "code": "nib-corp-ncins",
+      "name": "НИБ. Страхование",
+      "isDeleted": false,
+      "category": "RECEIVE",
+      "type": "BANK_SYSTEM"
+    }
+  ],
+  "participants": [
+    {
+      "id": "bdec62a5-e10a-4c5b-86c7-b5ac190b8055",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "isDeleted": false,
+      "contacts": [
+        {
+          "type": "EMAIL",
+          "typeName": "Email",
+          "value": "romashka@rambler.ru",
+          "isPrimary": false
+        },
+        {
+          "type": "PHONE",
+          "typeName": "Телефон",
+          "value": "79183221488",
+          "isPrimary": false
+        }
+      ],
+      "addresses": [
+        {
+          "type": "FACT",
+          "typeName": "Адрес проживания / фактический - краткий",
+          "address": {
+            "fullAddress": "Г. Пушкино ул. Колотушкина д. 14/88"
+          }
+        }
+      ],
+      "identityDocuments": [],
+      "okveds": [],
+      "licenses": [],
+      "management": [],
+      "founders": [],
+      "externalPins": [],
+      "pin": "AAAXYX",
+      "type": "LEGAL",
+      "typeName": "Юридическое лицо",
+      "fullName": "ООО Звезда",
+      "inn": "7826688577",
+      "createDate": "2026-07-09T17:19:18.963685Z",
+      "lastUpdateDate": "2026-07-09T17:19:19.99786Z",
+      "citizenship": "Россия",
+      "citizenshipCode": "RU",
+      "taxCountryCode": "RU",
+      "ogrn": "1027810281740"
+    }
+  ],
+  "products": [
+    {
+      "id": "3d9fe175-2bc5-442a-b900-48522551de3f",
+      "applicationId": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+      "status": {
+        "isTerminate": true,
+        "code": "COMPLETE",
+        "name": "Завершен"
+      },
+      "stage": {
+        "code": "PAYMENT_COMPLETED",
+        "name": "PAYMENT_COMPLETED"
+      },
+      "createDate": "2026-07-09T17:19:18.891861Z",
+      "lastUpdateDate": "2026-07-09T17:23:50.600316Z",
+      "code": "NON_CREDIT_INSURANCE",
+      "name": "Некредитное страхование ЮЛ",
+      "type": "PRODUCT",
+      "main": false,
+      "isDeleted": false,
+      "responsibleManager": {
+        "login": "U_M13RU"
+      },
+      "salesChannel": {
+        "code": "SFA",
+        "name": "SFA"
+      },
+      "productProperties": {
+        "programId": 1073741824,
+        "beginDate": "2026-06-25T11:47:13.57Z",
+        "endDate": "2026-06-25T11:47:13.57Z",
+        "signDate": "2026-06-25T11:47:13.57Z",
+        "duration": 12,
+        "insuranceSum": 20000.0,
+        "insurancePremium": 20000.0,
+        "contractNumber": "1423423/sdf/123",
+        "paymentType": "payment_account",
+        "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+        "insuranceObjects": [
+          {
+            "paymentAccount": "123523464567347"
+          }
+        ],
+        "code": "NON_CREDIT_INSURANCE"
+      },
+      "channelCode": "nib-corp-ncins"
+    }
+  ],
+  "options": [],
+  "id": "6dc5daf3-da12-4aae-9766-572da7b6b003",
+  "createDate": "2026-07-09T17:19:18.833504Z",
+  "lastUpdateDate": "2026-07-09T17:22:46.462517Z",
+  "number": "UMP26070994592",
+  "statusCode": "COMPLETE",
+  "statusName": "Завершена",
+  "finalVersion": true,
+  "isDeleted": false
+}
+Camunda job output (успех):
+{ "getProcessParams": "SUCCESS", ...поля по processType из ApplicationMapper }
+Ошибка:
+{ "getProcessParams": "ERROR" }</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>ApplicationDataWorkerIT
+stubs/ump/ump_application_response_200.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="372" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>ump-prepare-documents-ncins-pa.get-report-data</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>PrepareDataForPrintFormWorker</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>нет HTTP (XML+Base64)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>fullName/inn/email/contractNumber/sums/paymentAccount (IT)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>documents[0].documentType=CONTRACT_ACCOUNT_BLOCK, reportData=Base64</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="70" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>ump-prepare-documents-ncins-pa.get-report-data
+(локально XML→Base64)</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>PrepareDataForPrintFormWorker
+prepare</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>JobWorker: ump-prepare-documents-ncins-pa.get-report-data
+HTTP: нет (локальная сборка XML + Base64)
+Camunda input (PrepareDataForPrintFormWorkerIT):
+{
+  "businessKey": "550e8400-e29b-41d4-a716-446655110003",
+  "programId": 1,
+  "fullName": "Иванов Иван Иванович",
+  "inn": "123456789012",
+  "email": "ivanov@example.com",
+  "contractNumber": "NC-2025-001",
+  "beginDate": "2025-01-01T00:00:00+03:00",
+  "endDate": "2026-01-01T00:00:00+03:00",
+  "currentDate": "2025-01-15",
+  "insuranceSum": 1000000.0,
+  "insurancePremium": 50000.0,
+  "paymentAccount": "40817810000000000001"
+}</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Camunda output:
+{
+  "serviceId": "550e8400-e29b-41d4-a716-446655110003",
+  "serviceCode": "APPLICATION",
+  "productCode": "NON_CREDIT_INSURANCE",
+  "documents": [
+    {
+      "documentType": "CONTRACT_ACCOUNT_BLOCK",
+      "reportData": "&lt;Base64 от XML ниже&gt;",
+      "isWriteInEa": false
+    }
+  ]
+}
+XML до Base64 (IT assert):
+&lt;?xml version="1.0" encoding="UTF-8"?&gt;
+&lt;datasource&gt;
+  &lt;contractNumber&gt;NC-2025-001&lt;/contractNumber&gt;
+  &lt;fullName&gt;Иванов Иван Иванович&lt;/fullName&gt;
+  &lt;inn&gt;123456789012&lt;/inn&gt;
+  &lt;email&gt;ivanov@example.com&lt;/email&gt;
+  &lt;paymentAccount&gt;40817810000000000001&lt;/paymentAccount&gt;
+  &lt;insuranceSum&gt;1000000.00&lt;/insuranceSum&gt;
+  &lt;insurancePremium&gt;50000.00&lt;/insurancePremium&gt;
+  &lt;beginDate&gt;...&lt;/beginDate&gt;
+  &lt;endDate&gt;...&lt;/endDate&gt;
+  &lt;currentDate&gt;2025-01-15&lt;/currentDate&gt;
+&lt;/datasource&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>PrepareDataForPrintFormWorkerIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="332" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Call Activity</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>ump-generate-and-save-document-pa</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>внешний процесс</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>serviceId=businessKey, serviceCode=APPLICATION, documents</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>acDocuments, acRequestId, docsResult</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>update-product
+PUT /products/{id}</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>ProductDataUpdateWorker
+prepare</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>PUT /products/3d9fe175-2bc5-442a-b900-48522551de3f HTTP/1.1
+Host: ump-products.ump.svc.cluster.local
+Content-Type: application/json
+{
+  "code": "NON_CREDIT_INSURANCE",
+  "name": "Некредитное страхование ЮЛ",
+  "productProperties": {
+    "code": "NON_CREDIT_INSURANCE",
+    "programId": 1073741824,
+    "contractNumber": "1423423/sdf/123",
+    "beginDate": "2026-06-25T11:47:13.57Z",
+    "endDate": "2026-06-25T11:47:13.57Z",
+    "signDate": "2026-06-25T11:47:13.57Z",
+    "duration": 12,
+    "insuranceSum": 20000.0,
+    "insurancePremium": 20000.0,
+    "paymentType": "payment_account",
+    "agreementLink": "7ca85f64-5717-4562-b3fc-6c163f65aba9",
+    "policyLink": "770e8400-e29b-41d4-a716-446655110002",
+    "insuranceObjects": [
+      {
+        "paymentAccount": "123523464567347"
+      }
+    ]
+  }
+}
+Примечание: body = ProductCommonParamDto из productInfo;
+worker ДО вызова ставит productProperties.policyLink = acDocuments[0].acId.
+Живого JSON в IT нет (Mockito) — тело собрано по stub заявки + логике ProductDataUpdateWorker.</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>HTTP/1.1 200 OK
+Content-Type: application/json
+ProductDto (возврат Feign; в IT не зафиксирован literal — обычно эхо обновлённого продукта).
+Camunda job output:
+{ "getProcessParams": "SUCCESS" }
+При exception:
+{ "getProcessParams": "ERROR" }</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>ProductDataUpdateWorker + stub заявки
+(IT без literal PUT body)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>update-product</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>ProductDataUpdateWorker</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>PUT /products/{id}</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>{"productId":"660e...","acDocuments":[{"type":"CONTRACT_ACCOUNT_BLOCK","acId":"770e..."}],"productInfo":{}}</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>{"getProcessParams":"SUCCESS"}</t>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Call Activity ump-generate-and-save-document-pa</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>внешний процесс
+prepare</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>calledElement inputs:
+{
+  "serviceId": "&lt;businessKey&gt;",
+  "serviceCode": "APPLICATION",
+  "productCode": "&lt;productCode&gt;",
+  "documents": [ { "documentType": "CONTRACT_ACCOUNT_BLOCK", "reportData": "&lt;Base64&gt;", "isWriteInEa": false } ]
+}
+Полный HTTP ПФ/AC — во внешнем процессе (не в ump-ncins-pa).</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>outputs:
+{
+  "docsResult": "&lt;result&gt;",
+  "acRequestId": "&lt;...&gt;",
+  "acDocuments": [ { "type": "CONTRACT_ACCOUNT_BLOCK", "acId": "&lt;uuid&gt;" } ]
+}</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>BPMN prepare Call Activity</t>
         </is>
       </c>
     </row>
